--- a/intern_schedule_2026-2027/schedules/TYP_January_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_January_2027.xlsx
@@ -517,17 +517,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, SALAM</t>
+          <t>ZAIDI H, SALAM M</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
     </row>
@@ -542,13 +542,13 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>SALAM  (24H)</t>
+          <t>SALAM M  (24H)</t>
         </is>
       </c>
     </row>
@@ -563,13 +563,13 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>FARZEELA</t>
+          <t>FARZEELA F</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -584,17 +584,17 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>AHN, SALAM</t>
+          <t>AHN H, SALAM M</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -609,17 +609,17 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, SALAM</t>
+          <t>OGHENESUME O, SALAM M</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, AHN</t>
+          <t>OGHENESUME O, AHN H</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -659,17 +659,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>AHN, SALAM</t>
+          <t>AHN H, SALAM M</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
     </row>
@@ -709,13 +709,13 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>AHN  (24H)</t>
+          <t>AHN H  (24H)</t>
         </is>
       </c>
     </row>
@@ -730,13 +730,13 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>SALAM</t>
+          <t>SALAM M</t>
         </is>
       </c>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -751,17 +751,17 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>AHN, JUYAL</t>
+          <t>AHN H, JUYAL S</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, AHN</t>
+          <t>ZAIDI H, AHN H</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -801,17 +801,17 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, JUYAL</t>
+          <t>ZAIDI H, JUYAL S</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -851,17 +851,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, JUYAL</t>
+          <t>ZAIDI H, JUYAL S</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
     </row>
@@ -876,13 +876,13 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI  (24H)</t>
+          <t>ZAIDI H  (24H)</t>
         </is>
       </c>
     </row>
@@ -897,13 +897,13 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, JUYAL</t>
+          <t>ZAIDI H, JUYAL S</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, JUYAL</t>
+          <t>OGHENESUME O, JUYAL S</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -968,17 +968,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, OGHENESUME</t>
+          <t>ZAIDI H, OGHENESUME O</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, OGHENESUME</t>
+          <t>ZAIDI H, OGHENESUME O</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
     </row>
@@ -1043,13 +1043,13 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME  (24H)</t>
+          <t>OGHENESUME O  (24H)</t>
         </is>
       </c>
     </row>
@@ -1064,13 +1064,13 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -1085,17 +1085,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, AHN</t>
+          <t>OGHENESUME O, AHN H</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, AHN</t>
+          <t>ZAIDI H, AHN H</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -1135,17 +1135,17 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI, OGHENESUME</t>
+          <t>ZAIDI H, OGHENESUME O</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>OGHENESUME O</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -1185,17 +1185,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>OGHENESUME, AHN</t>
+          <t>OGHENESUME O, AHN H</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>
@@ -1210,13 +1210,13 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>AHN</t>
+          <t>AHN H</t>
         </is>
       </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>AHN  (24H)</t>
+          <t>AHN H  (24H)</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>ZAIDI H</t>
         </is>
       </c>
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>JUYAL</t>
+          <t>JUYAL S</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_January_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_January_2027.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
       <i val="1"/>
@@ -78,23 +79,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,61 +519,61 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, SALAM M</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, FARZEELA</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>SALAM M  (24H)</t>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>FARZEELA</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>FARZEELA  (24H)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>FARZEELA F</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -582,19 +586,19 @@
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>AHN H, SALAM M</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>AHN, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -607,19 +611,19 @@
       <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, SALAM M</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SALAM, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -632,19 +636,19 @@
       <c r="B8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, AHN H</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SALAM, AHN</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -657,19 +661,19 @@
       <c r="B9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -682,61 +686,61 @@
       <c r="B10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>AHN H, SALAM M</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>SALAM, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>AHN H  (24H)</t>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>ZAIDI  (24H)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>SALAM M</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>SALAM</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
@@ -749,19 +753,19 @@
       <c r="B13" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>AHN H, JUYAL S</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, JUYAL</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
@@ -774,19 +778,19 @@
       <c r="B14" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, AHN H</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, JUYAL</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
@@ -799,19 +803,19 @@
       <c r="B15" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, JUYAL S</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, ZAIDI</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
@@ -824,19 +828,19 @@
       <c r="B16" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
@@ -849,61 +853,61 @@
       <c r="B17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, JUYAL S</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, JUYAL</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>ZAIDI H  (24H)</t>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>JUYAL  (24H)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -916,19 +920,19 @@
       <c r="B20" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, JUYAL S</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -941,19 +945,19 @@
       <c r="B21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, JUYAL S</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>AHN, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -966,19 +970,19 @@
       <c r="B22" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>AHN, JUYAL</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -991,19 +995,19 @@
       <c r="B23" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -1016,61 +1020,61 @@
       <c r="B24" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>AHN, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>OGHENESUME O  (24H)</t>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>OGHENESUME  (24H)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
@@ -1083,19 +1087,19 @@
       <c r="B27" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, AHN H</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME, AHN</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
@@ -1108,19 +1112,19 @@
       <c r="B28" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, AHN H</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, AHN</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
@@ -1133,19 +1137,19 @@
       <c r="B29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H, OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
@@ -1158,19 +1162,19 @@
       <c r="B30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
@@ -1183,78 +1187,78 @@
       <c r="B31" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>OGHENESUME O, AHN H</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>ZAIDI, AHN</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>JUYAL</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>AHN H</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>AHN H  (24H)</t>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>AHN</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>AHN  (24H)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>ZAIDI H</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>JUYAL S</t>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>ZAIDI</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -1285,7 +1289,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -1316,7 +1320,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -1347,7 +1351,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -1378,7 +1382,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>

--- a/intern_schedule_2026-2027/schedules/TYP_January_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_January_2027.xlsx
@@ -521,12 +521,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, FARZEELA</t>
+          <t>OGHENESUME, FARZEELA</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -567,13 +567,13 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>AHN, ZAIDI</t>
+          <t>AHN, OGHENESUME</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -618,12 +618,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>SALAM, ZAIDI</t>
+          <t>SALAM, OGHENESUME</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -693,12 +693,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>SALAM, ZAIDI</t>
+          <t>SALAM, OGHENESUME</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -713,13 +713,13 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>ZAIDI  (24H)</t>
+          <t>OGHENESUME  (24H)</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, JUYAL</t>
+          <t>OGHENESUME, JUYAL</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME, JUYAL</t>
+          <t>ZAIDI, JUYAL</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME, ZAIDI</t>
+          <t>ZAIDI, OGHENESUME</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME, JUYAL</t>
+          <t>ZAIDI, JUYAL</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -901,13 +901,13 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>JUYAL, OGHENESUME</t>
+          <t>JUYAL, ZAIDI</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>AHN, OGHENESUME</t>
+          <t>AHN, ZAIDI</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>AHN, OGHENESUME</t>
+          <t>AHN, ZAIDI</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
     </row>
@@ -1047,13 +1047,13 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>OGHENESUME  (24H)</t>
+          <t>ZAIDI  (24H)</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME, AHN</t>
+          <t>ZAIDI, AHN</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, AHN</t>
+          <t>OGHENESUME, AHN</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, OGHENESUME</t>
+          <t>OGHENESUME, ZAIDI</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>ZAIDI, AHN</t>
+          <t>OGHENESUME, AHN</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1235,13 +1235,13 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>ZAIDI</t>
+          <t>OGHENESUME</t>
         </is>
       </c>
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>ZAIDI</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>Humza Zaidi</t>
+          <t>Oghenewoma Oghenesume</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oghenewoma Oghenesume</t>
+          <t>Humza Zaidi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">

--- a/intern_schedule_2026-2027/schedules/TYP_January_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_January_2027.xlsx
@@ -1235,7 +1235,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>OGHENESUME</t>
+          <t>JUYAL</t>
         </is>
       </c>
       <c r="D33" s="6" t="n"/>
